--- a/output/pdf_financials_xlsx/HAY.xlsx
+++ b/output/pdf_financials_xlsx/HAY.xlsx
@@ -1337,31 +1337,31 @@
         <v>-1.607319</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.81469</v>
+        <v>-0.81469</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.44089</v>
+        <v>-2.44089</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.24177</v>
+        <v>-1.24177</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>3.60505</v>
+        <v>-3.60505</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.7346819999999999</v>
+        <v>-0.7346819999999999</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.988528</v>
+        <v>-0.988528</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>3.94331</v>
+        <v>-3.94331</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.230482</v>
+        <v>-1.230482</v>
       </c>
     </row>
     <row r="17">
@@ -1645,31 +1645,31 @@
         <v>-1.607319</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.81469</v>
+        <v>-0.81469</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.44089</v>
+        <v>-2.44089</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.24177</v>
+        <v>-1.24177</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>3.60505</v>
+        <v>-3.60505</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.7346819999999999</v>
+        <v>-0.7346819999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.988528</v>
+        <v>-0.988528</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>3.94331</v>
+        <v>-3.94331</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.230482</v>
+        <v>-1.230482</v>
       </c>
     </row>
     <row r="21">
@@ -1831,31 +1831,31 @@
         <v>-1.607319</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.81469</v>
+        <v>-0.81469</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.44089</v>
+        <v>-2.44089</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.24177</v>
+        <v>-1.24177</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3.60505</v>
+        <v>-3.60505</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.7346819999999999</v>
+        <v>-0.7346819999999999</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.988528</v>
+        <v>-0.988528</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>3.94331</v>
+        <v>-3.94331</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.230482</v>
+        <v>-1.230482</v>
       </c>
     </row>
     <row r="24">
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>27.156333</v>
+        <v>-27.156333</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>48.8178</v>
+        <v>-48.8178</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>62.0885</v>
+        <v>-62.0885</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>10.014028</v>
+        <v>-10.014028</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>14.69364</v>
+        <v>-14.69364</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>24.7132</v>
+        <v>-24.7132</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>30.333154</v>
+        <v>-30.333154</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>61.5241</v>
+        <v>-61.5241</v>
       </c>
     </row>
     <row r="27">
@@ -2081,31 +2081,31 @@
         <v>-1.607319</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.81469</v>
+        <v>-0.81469</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.44089</v>
+        <v>-2.44089</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.24177</v>
+        <v>-1.24177</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>3.60505</v>
+        <v>-3.60505</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.7346819999999999</v>
+        <v>-0.7346819999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.988528</v>
+        <v>-0.988528</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.94331</v>
+        <v>-3.94331</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.230482</v>
+        <v>-1.230482</v>
       </c>
     </row>
     <row r="28">
@@ -2205,31 +2205,31 @@
         <v>-1.607319</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.815222</v>
+        <v>-0.814158</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.445259</v>
+        <v>-2.436521</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.248109</v>
+        <v>-1.235431</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>3.614249</v>
+        <v>-3.595851</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.743324</v>
+        <v>-0.72604</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.995835</v>
+        <v>-0.981221</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.947856</v>
+        <v>-3.938764</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.232022</v>
+        <v>-1.228942</v>
       </c>
     </row>
     <row r="30">
@@ -2359,31 +2359,31 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6007,28 +6007,28 @@
         <v>0.116309</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.566416</v>
+        <v>0.384104</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.7470909999999999</v>
+        <v>0.489904</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.57262</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.57262</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.57262</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.943497</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.943497</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.943497</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -6414,28 +6414,28 @@
         <v>-0.024554</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.81469</v>
+        <v>-0.81469</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>2.44089</v>
+        <v>-2.44089</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>1.24177</v>
+        <v>-1.24177</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>3.60505</v>
+        <v>-3.60505</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.7346819999999999</v>
+        <v>-0.7346819999999999</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.988528</v>
+        <v>-0.988528</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>3.94331</v>
+        <v>-3.94331</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>1.230482</v>
+        <v>-1.230482</v>
       </c>
     </row>
     <row r="100">
@@ -7583,10 +7583,10 @@
         <v>0.004</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.217305</v>
+        <v>1.041517</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -15449,7 +15449,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -15548,7 +15552,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16358,7 +16366,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -16453,7 +16465,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -17546,7 +17562,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -26985,7 +27005,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -27597,7 +27621,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -28714,7 +28742,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -32981,31 +33013,31 @@
         </is>
       </c>
       <c r="M248" s="5" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="N248" s="5" t="n">
-        <v>0.81469</v>
+        <v>-0.81469</v>
       </c>
       <c r="O248" s="5" t="n">
-        <v>2.44089</v>
+        <v>-2.44089</v>
       </c>
       <c r="P248" s="5" t="n">
-        <v>1.24177</v>
+        <v>-1.24177</v>
       </c>
       <c r="Q248" s="5" t="n">
-        <v>3.60505</v>
+        <v>-3.60505</v>
       </c>
       <c r="R248" s="5" t="n">
-        <v>0.7346819999999999</v>
+        <v>-0.7346819999999999</v>
       </c>
       <c r="S248" s="5" t="n">
-        <v>0.988528</v>
+        <v>-0.988528</v>
       </c>
       <c r="T248" s="5" t="n">
-        <v>3.94331</v>
+        <v>-3.94331</v>
       </c>
       <c r="U248" s="5" t="n">
-        <v>1.230482</v>
+        <v>-1.230482</v>
       </c>
     </row>
     <row r="249">
@@ -33204,10 +33236,10 @@
         </is>
       </c>
       <c r="T250" s="5" t="n">
-        <v>3.943798</v>
+        <v>-3.943798</v>
       </c>
       <c r="U250" s="5" t="n">
-        <v>1.179176</v>
+        <v>-1.179176</v>
       </c>
     </row>
     <row r="251">
@@ -36244,28 +36276,28 @@
         </is>
       </c>
       <c r="M281" s="5" t="n">
-        <v>0.024554</v>
+        <v>-0.024554</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>0.827493</v>
+        <v>-0.827493</v>
       </c>
       <c r="O281" s="5" t="n">
-        <v>2.347703</v>
+        <v>-2.347703</v>
       </c>
       <c r="P281" s="5" t="n">
-        <v>1.082536</v>
+        <v>-1.082536</v>
       </c>
       <c r="Q281" s="5" t="n">
-        <v>3.851464</v>
+        <v>-3.851464</v>
       </c>
       <c r="R281" s="5" t="n">
-        <v>0.7453340000000001</v>
+        <v>-0.7453340000000001</v>
       </c>
       <c r="S281" s="5" t="n">
-        <v>0.79191</v>
+        <v>-0.79191</v>
       </c>
       <c r="T281" s="5" t="n">
-        <v>3.943798</v>
+        <v>-3.943798</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HAY.xlsx
+++ b/output/pdf_financials_xlsx/HAY.xlsx
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003166</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001509</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00023</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1092,28 +1092,28 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004288</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008691000000000001</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006497</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000371</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006437</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007761</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018879</v>
       </c>
     </row>
     <row r="13">
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.045864</v>
+        <v>-1.04903</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.7958150000000001</v>
+        <v>-0.797324</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.63113</v>
+        <v>-0.63136</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.745673</v>
@@ -2084,28 +2084,28 @@
         <v>-0.024554</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.81469</v>
+        <v>-0.810402</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.44089</v>
+        <v>-2.432199</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.24177</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.60505</v>
+        <v>-3.598553</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.7346819999999999</v>
+        <v>-0.734311</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.988528</v>
+        <v>-0.982091</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.94331</v>
+        <v>-3.935549</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.230482</v>
+        <v>-1.211603</v>
       </c>
     </row>
     <row r="28">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.045864</v>
+        <v>-1.04903</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.7958150000000001</v>
+        <v>-0.797324</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.63113</v>
+        <v>-0.63136</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.745673</v>
@@ -2208,28 +2208,28 @@
         <v>-0.024554</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.814158</v>
+        <v>-0.80987</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.436521</v>
+        <v>-2.42783</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.235431</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.595851</v>
+        <v>-3.589354</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.72604</v>
+        <v>-0.725669</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.981221</v>
+        <v>-0.974784</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.938764</v>
+        <v>-3.931003</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.228942</v>
+        <v>-1.210063</v>
       </c>
     </row>
     <row r="30">
@@ -2504,16 +2504,16 @@
         <v>0.124146</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.069369</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.016889</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.01944</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001166</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.021916</v>
@@ -2620,16 +2620,16 @@
         <v>0.124146</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.069369</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.016889</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.01944</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001166</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.021916</v>
@@ -3316,16 +3316,16 @@
         <v>0.07871499999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.07615</v>
+        <v>0.006781</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.016411</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.03989</v>
+        <v>0.02045</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.001166</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -32371,7 +32371,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -51196,7 +51196,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -53994,7 +53994,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
